--- a/artfynd/A 44074-2023 artfynd.xlsx
+++ b/artfynd/A 44074-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 44074-2023 artfynd.xlsx
+++ b/artfynd/A 44074-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>71821158</v>
+        <v>109808590</v>
       </c>
       <c r="B2" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,40 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222771</v>
+        <v>1205</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Grundfors, Ly lm</t>
+          <t>Raningen, Grundfors, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>623982.2077019816</v>
+        <v>623973</v>
       </c>
       <c r="R2" t="n">
-        <v>7206138.060226545</v>
+        <v>7206169</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-06-07</t>
+          <t>2023-06-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-06-07</t>
+          <t>2023-06-02</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,62 +770,66 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Emil Larsson, Anna Hallmén</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>109808590</v>
+        <v>117613912</v>
       </c>
       <c r="B3" t="n">
-        <v>89403</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58238</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1205</v>
+        <v>103012</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Raningen, Grundfors, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>623972.8317590153</v>
+        <v>624193</v>
       </c>
       <c r="R3" t="n">
-        <v>7206169.488850757</v>
+        <v>7206155</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -860,22 +856,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,12 +901,7 @@
         <v>109808592</v>
       </c>
       <c r="B4" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -942,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>623985.7810895264</v>
+        <v>623986</v>
       </c>
       <c r="R4" t="n">
-        <v>7206164.511689191</v>
+        <v>7206165</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1014,15 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>109808589</v>
+        <v>71821158</v>
       </c>
       <c r="B5" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1048,19 +1034,22 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Raningen, Grundfors, Ly lm</t>
+          <t>Grundfors, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>623977.8496237957</v>
+        <v>623982</v>
       </c>
       <c r="R5" t="n">
-        <v>7206171.394259183</v>
+        <v>7206138</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1084,22 +1073,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>10:45</t>
+          <t>2018-06-07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>10:45</t>
+          <t>2018-06-07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,22 +1087,129 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Emil Larsson, Anna Hallmén</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>109808589</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Raningen, Grundfors, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>623978</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7206171</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Isak Vahlström</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Isak Vahlström</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
